--- a/scenario/Warehouse_lightweight.xlsx
+++ b/scenario/Warehouse_lightweight.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="s:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECDEDA8-3062-469B-A02C-D70809E67D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E344D9-334A-4611-89A9-DB9E558AB945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4697" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4703" uniqueCount="1385">
   <si>
     <t>Scenario name</t>
   </si>
@@ -25013,10 +25013,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -25033,7 +25033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -25049,8 +25049,11 @@
       <c r="E2" s="1" t="s">
         <v>1384</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1369</v>
       </c>
@@ -25066,8 +25069,11 @@
       <c r="E3" t="s">
         <v>1360</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1370</v>
       </c>
@@ -25083,8 +25089,11 @@
       <c r="E4" t="s">
         <v>1360</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1371</v>
       </c>
@@ -25100,8 +25109,11 @@
       <c r="E5" t="s">
         <v>1360</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1372</v>
       </c>
@@ -25117,8 +25129,11 @@
       <c r="E6" t="s">
         <v>1360</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1373</v>
       </c>
@@ -25133,6 +25148,9 @@
       </c>
       <c r="E7" t="s">
         <v>1360</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1373</v>
       </c>
     </row>
   </sheetData>

--- a/scenario/Warehouse_lightweight.xlsx
+++ b/scenario/Warehouse_lightweight.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="s:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Amalgama 2.0\github\warehouse-tutorial\scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E344D9-334A-4611-89A9-DB9E558AB945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459F5D81-5CCB-40FA-A12D-D7272F8FF080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet name="Point" sheetId="5" r:id="rId5"/>
     <sheet name="Forklift" sheetId="6" r:id="rId6"/>
     <sheet name="Gate" sheetId="7" r:id="rId7"/>
-    <sheet name="Gate_places" sheetId="8" r:id="rId8"/>
+    <sheet name="Gate_storagePlaces" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4703" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4703" uniqueCount="1384">
   <si>
     <t>Scenario name</t>
   </si>
@@ -4176,9 +4176,6 @@
   </si>
   <si>
     <t>Gate</t>
-  </si>
-  <si>
-    <t>places</t>
   </si>
   <si>
     <t>basePosition</t>
@@ -25047,7 +25044,7 @@
         <v>1376</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>206</v>
@@ -25225,12 +25222,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1382</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1383</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">

--- a/scenario/Warehouse_lightweight.xlsx
+++ b/scenario/Warehouse_lightweight.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Amalgama 2.0\github\warehouse-tutorial\scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459F5D81-5CCB-40FA-A12D-D7272F8FF080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12525B52-868C-404C-A961-F057F33CF6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4703" uniqueCount="1384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4837" uniqueCount="1387">
   <si>
     <t>Scenario name</t>
   </si>
@@ -4179,6 +4179,15 @@
   </si>
   <si>
     <t>basePosition</t>
+  </si>
+  <si>
+    <t>Gate-1</t>
+  </si>
+  <si>
+    <t>Gate-3</t>
+  </si>
+  <si>
+    <t>OUT</t>
   </si>
 </sst>
 </file>
@@ -25157,7 +25166,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -25195,13 +25204,35 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>1378</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>1380</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>1077</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -25211,7 +25242,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -25488,258 +25519,770 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B35" t="s">
-        <v>1262</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B36" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B37" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B38" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B39" t="s">
-        <v>1263</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B40" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B41" t="s">
-        <v>1330</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B42" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B43" t="s">
-        <v>1264</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B44" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B45" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B46" t="s">
-        <v>1333</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B47" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B48" t="s">
-        <v>1273</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B49" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B50" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B51" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B52" t="s">
-        <v>1274</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B53" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B54" t="s">
-        <v>1337</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B55" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B56" t="s">
-        <v>1275</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B57" t="s">
-        <v>1338</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B58" t="s">
-        <v>1339</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B59" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B60" t="s">
-        <v>1276</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B61" t="s">
-        <v>1340</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B62" t="s">
-        <v>1341</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B63" t="s">
-        <v>1269</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B64" t="s">
-        <v>1277</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B65" t="s">
-        <v>1342</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>1378</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B98" t="s">
         <v>1343</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1359</v>
       </c>
     </row>
   </sheetData>
